--- a/Team-Data/2012-13/3-4-2012-13.xlsx
+++ b/Team-Data/2012-13/3-4-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
         <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -679,10 +746,10 @@
         <v>37.4</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L2" t="n">
         <v>9</v>
@@ -691,67 +758,67 @@
         <v>23.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.38</v>
+        <v>0.382</v>
       </c>
       <c r="O2" t="n">
         <v>13.7</v>
       </c>
       <c r="P2" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="R2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U2" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="V2" t="n">
         <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA2" t="n">
         <v>18.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
         <v>12</v>
@@ -769,16 +836,16 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
@@ -793,25 +860,25 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -930,7 +997,7 @@
         <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -945,13 +1012,13 @@
         <v>9</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
         <v>20</v>
@@ -978,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
         <v>24</v>
@@ -987,10 +1054,10 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>0.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1136,7 +1203,7 @@
         <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
         <v>9</v>
@@ -1145,7 +1212,7 @@
         <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
         <v>25</v>
@@ -1160,7 +1227,7 @@
         <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
@@ -1169,13 +1236,13 @@
         <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -1207,67 +1274,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>0.217</v>
+        <v>0.22</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="J5" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.419</v>
+        <v>0.418</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O5" t="n">
         <v>19.1</v>
       </c>
       <c r="P5" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="S5" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T5" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U5" t="n">
         <v>18.9</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.1</v>
       </c>
       <c r="X5" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y5" t="n">
         <v>7.5</v>
@@ -1276,16 +1343,16 @@
         <v>19.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-10.1</v>
+        <v>-10</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,25 +1364,25 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1327,22 +1394,22 @@
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS5" t="n">
         <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU5" t="n">
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
@@ -1497,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
         <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ6" t="n">
         <v>6</v>
@@ -1527,7 +1594,7 @@
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1589,10 +1656,10 @@
         <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L7" t="n">
         <v>7.1</v>
@@ -1610,19 +1677,19 @@
         <v>22.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R7" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S7" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="T7" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U7" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V7" t="n">
         <v>14.1</v>
@@ -1640,7 +1707,7 @@
         <v>21.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB7" t="n">
         <v>97.59999999999999</v>
@@ -1649,13 +1716,13 @@
         <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
         <v>26</v>
       </c>
       <c r="AF7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
         <v>27</v>
@@ -1664,19 +1731,19 @@
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>14</v>
       </c>
       <c r="AM7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN7" t="n">
         <v>19</v>
@@ -1691,37 +1758,37 @@
         <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AU7" t="n">
         <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY7" t="n">
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1849,10 +1916,10 @@
         <v>7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL8" t="n">
         <v>13</v>
@@ -1888,7 +1955,7 @@
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -1897,13 +1964,13 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -1935,43 +2002,43 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.639</v>
+        <v>0.633</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="J9" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L9" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N9" t="n">
         <v>0.339</v>
       </c>
       <c r="O9" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0.6899999999999999</v>
@@ -2004,19 +2071,19 @@
         <v>20.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB9" t="n">
         <v>105.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF9" t="n">
         <v>7</v>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2034,10 +2101,10 @@
         <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM9" t="n">
         <v>17</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -2207,16 +2274,16 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ10" t="n">
         <v>19</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
@@ -2237,22 +2304,22 @@
         <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
         <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J11" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L11" t="n">
         <v>7.9</v>
@@ -2329,28 +2396,28 @@
         <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.395</v>
+        <v>0.394</v>
       </c>
       <c r="O11" t="n">
         <v>17.3</v>
       </c>
       <c r="P11" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0.798</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S11" t="n">
         <v>33.7</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V11" t="n">
         <v>15.3</v>
@@ -2365,22 +2432,22 @@
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.3</v>
+        <v>100.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2389,7 +2456,7 @@
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI11" t="n">
         <v>9</v>
@@ -2398,22 +2465,22 @@
         <v>8</v>
       </c>
       <c r="AK11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2428,13 +2495,13 @@
         <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV11" t="n">
         <v>26</v>
       </c>
       <c r="AW11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
@@ -2446,10 +2513,10 @@
         <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -2562,16 +2629,16 @@
         <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG12" t="n">
         <v>14</v>
       </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2589,10 +2656,10 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP12" t="n">
         <v>6</v>
@@ -2601,7 +2668,7 @@
         <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2616,7 +2683,7 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
         <v>28</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>7</v>
       </c>
       <c r="AG13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
@@ -2810,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2944,7 +3011,7 @@
         <v>24</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
@@ -2962,7 +3029,7 @@
         <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>12</v>
@@ -2977,7 +3044,7 @@
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
         <v>5</v>
@@ -3174,7 +3241,7 @@
         <v>4</v>
       </c>
       <c r="BA15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB15" t="n">
         <v>6</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3302,10 +3369,10 @@
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK16" t="n">
         <v>22</v>
@@ -3320,7 +3387,7 @@
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP16" t="n">
         <v>24</v>
@@ -3341,7 +3408,7 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
         <v>3</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.759</v>
+        <v>0.754</v>
       </c>
       <c r="H17" t="n">
         <v>48.7</v>
@@ -3415,13 +3482,13 @@
         <v>0.496</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>21.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.391</v>
+        <v>0.393</v>
       </c>
       <c r="O17" t="n">
         <v>17.3</v>
@@ -3430,25 +3497,25 @@
         <v>22.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R17" t="n">
         <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T17" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="U17" t="n">
         <v>22.6</v>
       </c>
       <c r="V17" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="W17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X17" t="n">
         <v>5</v>
@@ -3457,19 +3524,19 @@
         <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.6</v>
+        <v>103.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3499,10 +3566,10 @@
         <v>8</v>
       </c>
       <c r="AN17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>14</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -3573,43 +3640,43 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18" t="n">
         <v>28</v>
       </c>
       <c r="G18" t="n">
-        <v>0.517</v>
+        <v>0.509</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J18" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="K18" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L18" t="n">
         <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O18" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.735</v>
@@ -3624,13 +3691,13 @@
         <v>43.8</v>
       </c>
       <c r="U18" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V18" t="n">
         <v>14.4</v>
       </c>
       <c r="W18" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X18" t="n">
         <v>7.4</v>
@@ -3639,31 +3706,31 @@
         <v>4.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA18" t="n">
         <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.5</v>
+        <v>98.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
         <v>8</v>
@@ -3675,7 +3742,7 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="n">
         <v>19</v>
@@ -3687,7 +3754,7 @@
         <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
         <v>23</v>
@@ -3708,7 +3775,7 @@
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="n">
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0.351</v>
+        <v>0.357</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,10 +3840,10 @@
         <v>35.4</v>
       </c>
       <c r="J19" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.433</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
         <v>5.3</v>
@@ -3785,34 +3852,34 @@
         <v>17.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.297</v>
+        <v>0.298</v>
       </c>
       <c r="O19" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P19" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R19" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S19" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="T19" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>4.9</v>
@@ -3824,13 +3891,13 @@
         <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3</v>
+        <v>-2.7</v>
       </c>
       <c r="AD19" t="n">
         <v>29</v>
@@ -3851,10 +3918,10 @@
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3866,7 +3933,7 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP19" t="n">
         <v>4</v>
@@ -3881,31 +3948,31 @@
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
         <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
         <v>12</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ19" t="n">
         <v>5</v>
       </c>
       <c r="BA19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
         <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>0.344</v>
+        <v>0.35</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3973,28 +4040,28 @@
         <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="Q20" t="n">
         <v>0.769</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S20" t="n">
         <v>29.8</v>
       </c>
       <c r="T20" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U20" t="n">
         <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W20" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X20" t="n">
         <v>5.6</v>
@@ -4009,25 +4076,25 @@
         <v>18.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC20" t="n">
         <v>-3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>21</v>
@@ -4036,7 +4103,7 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>17</v>
@@ -4051,13 +4118,13 @@
         <v>25</v>
       </c>
       <c r="AP20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS20" t="n">
         <v>24</v>
@@ -4078,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
         <v>20</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
         <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>0.632</v>
+        <v>0.625</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,7 +4204,7 @@
         <v>36.4</v>
       </c>
       <c r="J21" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K21" t="n">
         <v>0.442</v>
@@ -4158,22 +4225,22 @@
         <v>21.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R21" t="n">
         <v>11.2</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T21" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U21" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V21" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="W21" t="n">
         <v>8.1</v>
@@ -4218,7 +4285,7 @@
         <v>11</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
         <v>19</v>
@@ -4257,7 +4324,7 @@
         <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>5</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -4483,25 +4550,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F23" t="n">
         <v>44</v>
       </c>
       <c r="G23" t="n">
-        <v>0.279</v>
+        <v>0.267</v>
       </c>
       <c r="H23" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J23" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>0.453</v>
@@ -4522,7 +4589,7 @@
         <v>16.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R23" t="n">
         <v>10.5</v>
@@ -4531,13 +4598,13 @@
         <v>31.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U23" t="n">
         <v>23.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
         <v>6</v>
@@ -4546,22 +4613,22 @@
         <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z23" t="n">
         <v>19</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4588,7 +4655,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN23" t="n">
         <v>28</v>
@@ -4609,13 +4676,13 @@
         <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU23" t="n">
         <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4800,7 +4867,7 @@
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
         <v>23</v>
@@ -4946,7 +5013,7 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL25" t="n">
         <v>27</v>
@@ -4961,7 +5028,7 @@
         <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ25" t="n">
         <v>19</v>
@@ -4979,7 +5046,7 @@
         <v>15</v>
       </c>
       <c r="AV25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" t="n">
         <v>31</v>
       </c>
       <c r="G26" t="n">
-        <v>0.475</v>
+        <v>0.466</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
         <v>82.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.446</v>
+        <v>0.443</v>
       </c>
       <c r="L26" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
         <v>23.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.342</v>
+        <v>0.339</v>
       </c>
       <c r="O26" t="n">
         <v>16.3</v>
@@ -5068,7 +5135,7 @@
         <v>21</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R26" t="n">
         <v>11.3</v>
@@ -5080,10 +5147,10 @@
         <v>41.7</v>
       </c>
       <c r="U26" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V26" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W26" t="n">
         <v>6.9</v>
@@ -5098,16 +5165,16 @@
         <v>18.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.2</v>
+        <v>-2.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,16 +5186,16 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
         <v>12</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5137,10 +5204,10 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
         <v>23</v>
@@ -5161,13 +5228,13 @@
         <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5179,7 +5246,7 @@
         <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -5295,10 +5362,10 @@
         <v>23</v>
       </c>
       <c r="AF27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG27" t="n">
         <v>26</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>13</v>
@@ -5343,10 +5410,10 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -5501,13 +5568,13 @@
         <v>6</v>
       </c>
       <c r="AN28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5519,13 +5586,13 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G29" t="n">
-        <v>0.377</v>
+        <v>0.383</v>
       </c>
       <c r="H29" t="n">
         <v>48.9</v>
@@ -5593,7 +5660,7 @@
         <v>36.2</v>
       </c>
       <c r="J29" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
         <v>0.441</v>
@@ -5608,25 +5675,25 @@
         <v>0.349</v>
       </c>
       <c r="O29" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P29" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="R29" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S29" t="n">
         <v>29</v>
       </c>
       <c r="T29" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="U29" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V29" t="n">
         <v>13.2</v>
@@ -5644,16 +5711,16 @@
         <v>22.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5668,10 +5735,10 @@
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AK29" t="n">
         <v>20</v>
@@ -5695,7 +5762,7 @@
         <v>5</v>
       </c>
       <c r="AR29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS29" t="n">
         <v>28</v>
@@ -5710,10 +5777,10 @@
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
         <v>16</v>
@@ -5722,10 +5789,10 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -5757,97 +5824,97 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" t="n">
         <v>32</v>
       </c>
       <c r="F30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G30" t="n">
-        <v>0.533</v>
+        <v>0.542</v>
       </c>
       <c r="H30" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I30" t="n">
         <v>37</v>
       </c>
       <c r="J30" t="n">
-        <v>82.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L30" t="n">
         <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O30" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P30" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0.766</v>
       </c>
       <c r="R30" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T30" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="U30" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z30" t="n">
         <v>21.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
         <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI30" t="n">
         <v>14</v>
@@ -5856,16 +5923,16 @@
         <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5877,19 +5944,19 @@
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>9</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
         <v>11</v>
@@ -5901,7 +5968,7 @@
         <v>23</v>
       </c>
       <c r="AZ30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6035,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
@@ -6074,10 +6141,10 @@
         <v>28</v>
       </c>
       <c r="AW31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-4-2012-13</t>
+          <t>2013-03-04</t>
         </is>
       </c>
     </row>
